--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/8114-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/8114-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{863333CE-0072-4031-9BD7-E7BDB965E2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB716F88-1892-483F-A4A0-D9E809C27DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{80ECBCC7-F942-466D-A7F0-1DF79AB0B315}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{BA9D3BE9-8B8A-4545-8402-E53271E7DA5B}"/>
   </bookViews>
   <sheets>
     <sheet name="8114-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1481,25 +1481,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24A343CA-F3DE-4FC2-A709-EAD40E0F874E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BC7A383-7E15-4725-8695-85B74C23E81E}">
   <dimension ref="A1:X28"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1533,7 +1532,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1569,7 +1568,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1621,7 +1620,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1689,7 +1688,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1761,7 +1760,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>2023</v>
       </c>
@@ -1833,7 +1832,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>2022</v>
       </c>
@@ -1905,7 +1904,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2021</v>
       </c>
@@ -1977,7 +1976,7 @@
         <v>4.84</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>2020</v>
       </c>
@@ -2049,7 +2048,7 @@
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2019</v>
       </c>
@@ -2121,7 +2120,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>2018</v>
       </c>
@@ -2193,7 +2192,7 @@
         <v>6.46</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2017</v>
       </c>
@@ -2265,7 +2264,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>2016</v>
       </c>
@@ -2337,7 +2336,7 @@
         <v>6.46</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2015</v>
       </c>
@@ -2409,7 +2408,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="35">
         <v>2014</v>
       </c>
@@ -2481,7 +2480,7 @@
         <v>6.18</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2013</v>
       </c>
@@ -2553,7 +2552,7 @@
         <v>6.01</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2012</v>
       </c>
@@ -2625,7 +2624,7 @@
         <v>9.15</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2011</v>
       </c>
@@ -2697,7 +2696,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
         <v>2010</v>
       </c>
@@ -2769,7 +2768,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2009</v>
       </c>
@@ -2841,7 +2840,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="35">
         <v>2008</v>
       </c>
@@ -2913,7 +2912,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2007</v>
       </c>
@@ -2985,7 +2984,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>2006</v>
       </c>
@@ -3057,7 +3056,7 @@
         <v>8.48</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2005</v>
       </c>
@@ -3129,7 +3128,7 @@
         <v>6.48</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>2004</v>
       </c>
@@ -3201,7 +3200,7 @@
         <v>9.4700000000000006</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2003</v>
       </c>
@@ -3273,7 +3272,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2002</v>
       </c>
@@ -3345,7 +3344,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37" t="s">
         <v>51</v>
       </c>
